--- a/pacjenci/MAŁGORZATA STACHERA.xlsx
+++ b/pacjenci/MAŁGORZATA STACHERA.xlsx
@@ -483,10 +483,14 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -538,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>
@@ -618,7 +622,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/pacjenci/MAŁGORZATA STACHERA.xlsx
+++ b/pacjenci/MAŁGORZATA STACHERA.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>13.05.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak B-komórkowy. Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 79 mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne metabolicznie węzły chłonne szyjne: - grupy 1B po stronie prawej wielkości do 16x10 mm SUV max do 5,0; - grupy 2A po stronie lewej wielkości 8 mm SUV max 3,2; - grupy 2B po stronie lewej wielkości 8 mm SUV max 3,0; - grupy 4 po stronie lewej średnicy 6 mm SUV max 2,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja lewej zatoki czołowej, hypoplazja prawej.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny podostrogowy po stronie prawej, wielkości 13x9 mm wg PET SUV max 3,9.  Miernie pobudzone metabolicznie węzły chłonne: - międzypiersiowe lewe wielkości do 12x7 mm SUV max do 1,6; - pachowe lewe wielkości do 16x9 mm SUV max do 1,6; - pachowe prawe wielkości do 11x7 mm SUV max do 1,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, zwłaszcza od strony PK - o szerokości płaszcza do 11mm. Niewielkie zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywne metabolicznie obszary wielkości do 23x20 mm wg PET SUV max do 7,6 [Im fuz. 177] w znacznie powiększonej śledzionie [133x88x172mm], z rozlanie wzmożonym metabolizmem FDG. Aktywne metabolicznie węzły chłonne: - podwpustowo i przy krzywiźnie mniejszej żołądka wielkości do 25x9 mm SUV max do 4,1; - we wnęce śledziony oraz przy jej przyśrodkowo-tylnym obrysie, wielkości do 11x17 mm wg PET SUV max do 4,6; - okołoaortalne obustronnie na poziomie L1 wielkości do 10 mm SUV max do 4,0 [Im fuz. 157]; - okołoaortalne obustronnie i przedkręgosłupowe od poziomu L2 do poziomu rozwidlenia aorty, wielkości do 63x17x60 mm wg PET  SUV max do 15,1 [Im fuz. 178]; - przy naczyniach biodrowych wspólnych i wewnętrznych lewych, wielkości do 48x22 mm wg PET SUV max do [Im fuz. 215]; - przy naczyniach biodrowych zewnętrznych lewych wielkości do 55x93 mm wg PET SUV max do 16,3 [Im fuz. 220]; - przy naczyniach biodrowych wewnętrznych i zewnętrznych prawych wielkości do 13x9 mm SUV max do 4,7; - pachwinowe lewe - największy pakiet wielkości do 38x35x40 mm SUV max do 15,2; - pachwinowe prawe wielkości do 11x13 mm SUV max do 5,7. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W lewej pachwinie, w przyleganiu do aktywnego metabolicznie pakietu węzłowego widoczny jest pęcherz gazu wielkości 13x9mm - po BAC? zmiany zapalne/ropień? - do kontroli w USG.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Spłycenie fizjologicznych krzywizn kręgosłupa. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa [ciasna na poziomie C5/C6]. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Wyspa kostna w prawej kości kulszowej.  Wartości referencyjne: MBPS SUVmax 1,2; Prawy płat wątroby SUVmax do 2,3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem śledziony oraz bardzo licznych grup węzłów chłonnych po obu stronach przepony, zwłaszcza w jamie brzusznej i miednicy. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>16.3</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>26.07.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak B-komórkowy (DLBCL NOS ABC). Ocena odpowiedzi po 3 cyklach chemioimmunoterapii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 77 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja lewej zatoki czołowej, hypoplazja prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne: - międzypiersiowe lewe wielkości do 7 mm;  - pachowe lewe wielkości do 14x9 mm;  - pachowe prawe wielkości do 9 mm. Niewielkie zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Mierne pobudzenie metabolicznie w pachwinie lewej na obszarze wielkości 26x14x38 mm SUV max 1,6- w topografii opisywanego poprzednio pakietu węzłowego. Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 4,6- w pierwszej kolejności o charakterze odczynowym. Niejednorodny metabolizm FDG w śledzionie wielkości 124x57x138 mm. Wzmożony metabolizm FDG w topografii trzonu macicy SUV max do 3,7- do kontroli ginekologicznej (OM 09.2020) Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne: - okołoaortalne obustronnie wielkości do 22x14 mm; - przy naczyniach biodrowych wspólnych i wewnętrznych lewych, wielkości do18x12 mm; - przy naczyniach biodrowych zewnętrznych lewych wielkości do 19x22 mm ; - pachwinowe prawe wielkości do 7 mm. Ok. 10mm obwodowa hypodensyjna w przeglądowym badaniu TK zmiana w prawym płacie wątroby - torbielka?  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem SUV max do 3,1- w pierwszej kolejności wynikający ze stosowanego leczenia. Spłycenie fizjologicznych krzywizn kręgosłupa. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa [ciasna na poziomie C5/C6]. Zwapnienie w krążku międzykręgowym na poziomie L5/S1. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Wyspa kostna w prawej kości kulszowej.  Wartości referencyjne: MBPS SUVmax 1,4; Prawy płat wątroby SUVmax do 2,6.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź metaboliczną choroby na stosowane leczenie z częściową regresją zmian radiologicznych. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>4.6</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>04.10.2021</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak B-komórkowy (DLBCL NOS ABC). Ocena remisji choroby po zakończeniu ChTh.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 68 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja lewej zatoki czołowej, hypoplazja prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne węzły chłonne pachowe obustronnie. Niewielkie zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo. Drobny obwodowy pęcherz rozedmowy w segm. 6 płuca lewego.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 3,8- w pierwszej kolejności o charakterze odczynowym. Niejednorodny metabolizm FDG w śledzionie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zmiany włókniste w pachwinie lewej na obszarze wielkości 25x13 mm (SUV max 1,6). Śledziona powiększona: wielkości: 130x76x143mm. Ok. 11mm obwodowa hypodensyjna w przeglądowym badaniu TK zmiana w prawym płacie wątroby - torbielka?  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem - w pierwszej kolejności wynikający z zastosowanego leczenia. Spłycenie fizjologicznych krzywizn kręgosłupa. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa [ciasna na poziomie C5/C6]. Zwapnienie w krążku międzykręgowym na poziomie L5/S1. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Wyspa kostna w prawej kości kulszowej.  Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 2,8.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności  aktywnej metabolicznie choroby chłoniakowej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>3.8</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>31.01.2022</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak B-komórkowy (DLBCL NOS ABC). Ocena remisji choroby po zakończeniu ChTh.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58min od podania 18F-FDG. Glikemia: 99mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Aktywne metabolicznie węzły chłonne grup: - 2A po stronie lewej wielkości wg PET do 16x28mm, SUV max 21,0, - 2A po stronie prawej wielkości wg PET 20x27mm, SUV max 23,2. Symetryczna aktywność metaboliczna w fałdach głosowych, SUV max 4,2 - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja lewej zatoki czołowej, hypoplazja prawej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - przytchawicze prawe górne średnicy wg PET 20mm, SUV max 29,8, - w śródpiersiu tylnym obustronnie na wysokości trzonów kręgów Th2-Th4 o łącznej wielkości wg PET 33x28x46mm, SUV max 35,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne węzły chłonne pachowe obustronnie. Niewielkie zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo. Drobny obwodowy pęcherz rozedmowy w segm. 6 płuca lewego.  Brzuch i miednica: Aktywny metabolicznie pakiet węzłowy we wnęce wątroby średnicy wg PET 30mm, SUV max 19,0. Niejednorodny metabolizm FDG w śledzionie. Rozlana aktywność metaboliczna we wstępnicy, SUV max do 7,3 - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zmiany włókniste w pachwinie lewej na obszarze wielkości 25x13mm (SUV max 1,6). Śledziona powiększona w wymiarze dwubiegunowym 136mm. Ok. 11mm obwodowa hypodensyjna w przeglądowym badaniu TK zmiana w prawym płacie wątroby - torbielka?  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem - w pierwszej kolejności wynikający z zastosowanego leczenia. Spłycenie fizjologicznych krzywizn kręgosłupa. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa [ciasna na poziomie C5/C6]. Zwapnienie w krążku międzykręgowym na poziomie L5/S1. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Wyspa kostna w prawej kości kulszowej.  Wartości referencyjne: MBPS SUVmax 2,3; Prawy płat wątroby SUVmax do 3,2.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z zajęciem węzłów chłonnych po obu stronach przepony. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>35.6</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/MAŁGORZATA STACHERA.xlsx
+++ b/pacjenci/MAŁGORZATA STACHERA.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 79 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne szyjne: - grupy 1B po stronie prawej wielkości do 16x10 mm SUV max do 5,0; - grupy 2A po stronie lewej wielkości 8 mm SUV max 3,2; - grupy 2B po stronie lewej wielkości 8 mm SUV max 3,0; - grupy 4 po stronie lewej średnicy 6 mm SUV max 2,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja lewej zatoki czołowej, hypoplazja prawej.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny podostrogowy po stronie prawej, wielkości 13x9 mm wg PET SUV max 3,9.  Miernie pobudzone metabolicznie węzły chłonne: - międzypiersiowe lewe wielkości do 12x7 mm SUV max do 1,6; - pachowe lewe wielkości do 16x9 mm SUV max do 1,6; - pachowe prawe wielkości do 11x7 mm SUV max do 1,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, zwłaszcza od strony PK - o szerokości płaszcza do 11mm. Niewielkie zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywne metabolicznie obszary wielkości do 23x20 mm wg PET SUV max do 7,6 [Im fuz. 177] w znacznie powiększonej śledzionie [133x88x172mm], z rozlanie wzmożonym metabolizmem FDG. Aktywne metabolicznie węzły chłonne: - podwpustowo i przy krzywiźnie mniejszej żołądka wielkości do 25x9 mm SUV max do 4,1; - we wnęce śledziony oraz przy jej przyśrodkowo-tylnym obrysie, wielkości do 11x17 mm wg PET SUV max do 4,6; - okołoaortalne obustronnie na poziomie L1 wielkości do 10 mm SUV max do 4,0 [Im fuz. 157]; - okołoaortalne obustronnie i przedkręgosłupowe od poziomu L2 do poziomu rozwidlenia aorty, wielkości do 63x17x60 mm wg PET  SUV max do 15,1 [Im fuz. 178]; - przy naczyniach biodrowych wspólnych i wewnętrznych lewych, wielkości do 48x22 mm wg PET SUV max do [Im fuz. 215]; - przy naczyniach biodrowych zewnętrznych lewych wielkości do 55x93 mm wg PET SUV max do 16,3 [Im fuz. 220]; - przy naczyniach biodrowych wewnętrznych i zewnętrznych prawych wielkości do 13x9 mm SUV max do 4,7; - pachwinowe lewe - największy pakiet wielkości do 38x35x40 mm SUV max do 15,2; - pachwinowe prawe wielkości do 11x13 mm SUV max do 5,7. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W lewej pachwinie, w przyleganiu do aktywnego metabolicznie pakietu węzłowego widoczny jest pęcherz gazu wielkości 13x9mm - po BAC? zmiany zapalne/ropień? - do kontroli w USG.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Spłycenie fizjologicznych krzywizn kręgosłupa. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa [ciasna na poziomie C5/C6]. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Wyspa kostna w prawej kości kulszowej.  Wartości referencyjne: MBPS SUVmax 1,2; Prawy płat wątroby SUVmax do 2,3</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne szyjne: - grupy 1B po stronie prawej wielkości do 16x10 mm SUV max do 5,0; - grupy 2A po stronie lewej wielkości 8 mm SUV max 3,2; - grupy 2B po stronie lewej wielkości 8 mm SUV max 3,0; - grupy 4 po stronie lewej średnicy 6 mm SUV max 2,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja lewej zatoki czołowej, hypoplazja prawej.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny podostrogowy po stronie prawej, wielkości 13x9 mm wg PET SUV max 3,9.  Miernie pobudzone metabolicznie węzły chłonne: - międzypiersiowe lewe wielkości do 12x7 mm SUV max do 1,6; - pachowe lewe wielkości do 16x9 mm SUV max do 1,6; - pachowe prawe wielkości do 11x7 mm SUV max do 1,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, zwłaszcza od strony PK - o szerokości płaszcza do 11mm. Niewielkie zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie obszary wielkości do 23x20 mm wg PET SUV max do 7,6 [Im fuz. 177] w znacznie powiększonej śledzionie [133x88x172mm], z rozlanie wzmożonym metabolizmem FDG. Aktywne metabolicznie węzły chłonne: - podwpustowo i przy krzywiźnie mniejszej żołądka wielkości do 25x9 mm SUV max do 4,1; - we wnęce śledziony oraz przy jej przyśrodkowo-tylnym obrysie, wielkości do 11x17 mm wg PET SUV max do 4,6; - okołoaortalne obustronnie na poziomie L1 wielkości do 10 mm SUV max do 4,0 [Im fuz. 157]; - okołoaortalne obustronnie i przedkręgosłupowe od poziomu L2 do poziomu rozwidlenia aorty, wielkości do 63x17x60 mm wg PET  SUV max do 15,1 [Im fuz. 178]; - przy naczyniach biodrowych wspólnych i wewnętrznych lewych, wielkości do 48x22 mm wg PET SUV max do [Im fuz. 215]; - przy naczyniach biodrowych zewnętrznych lewych wielkości do 55x93 mm wg PET SUV max do 16,3 [Im fuz. 220]; - przy naczyniach biodrowych wewnętrznych i zewnętrznych prawych wielkości do 13x9 mm SUV max do 4,7; - pachwinowe lewe - największy pakiet wielkości do 38x35x40 mm SUV max do 15,2; - pachwinowe prawe wielkości do 11x13 mm SUV max do 5,7. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W lewej pachwinie, w przyleganiu do aktywnego metabolicznie pakietu węzłowego widoczny jest pęcherz gazu wielkości 13x9mm - po BAC? zmiany zapalne/ropień? - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Spłycenie fizjologicznych krzywizn kręgosłupa. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa [ciasna na poziomie C5/C6]. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Wyspa kostna w prawej kości kulszowej.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem śledziony oraz bardzo licznych grup węzłów chłonnych po obu stronach przepony, zwłaszcza w jamie brzusznej i miednicy. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>16.3</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 77 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja lewej zatoki czołowej, hypoplazja prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne: - międzypiersiowe lewe wielkości do 7 mm;  - pachowe lewe wielkości do 14x9 mm;  - pachowe prawe wielkości do 9 mm. Niewielkie zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Mierne pobudzenie metabolicznie w pachwinie lewej na obszarze wielkości 26x14x38 mm SUV max 1,6- w topografii opisywanego poprzednio pakietu węzłowego. Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 4,6- w pierwszej kolejności o charakterze odczynowym. Niejednorodny metabolizm FDG w śledzionie wielkości 124x57x138 mm. Wzmożony metabolizm FDG w topografii trzonu macicy SUV max do 3,7- do kontroli ginekologicznej (OM 09.2020) Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne: - okołoaortalne obustronnie wielkości do 22x14 mm; - przy naczyniach biodrowych wspólnych i wewnętrznych lewych, wielkości do18x12 mm; - przy naczyniach biodrowych zewnętrznych lewych wielkości do 19x22 mm ; - pachwinowe prawe wielkości do 7 mm. Ok. 10mm obwodowa hypodensyjna w przeglądowym badaniu TK zmiana w prawym płacie wątroby - torbielka?  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem SUV max do 3,1- w pierwszej kolejności wynikający ze stosowanego leczenia. Spłycenie fizjologicznych krzywizn kręgosłupa. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa [ciasna na poziomie C5/C6]. Zwapnienie w krążku międzykręgowym na poziomie L5/S1. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Wyspa kostna w prawej kości kulszowej.  Wartości referencyjne: MBPS SUVmax 1,4; Prawy płat wątroby SUVmax do 2,6.</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja lewej zatoki czołowej, hypoplazja prawej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne: - międzypiersiowe lewe wielkości do 7 mm;  - pachowe lewe wielkości do 14x9 mm;  - pachowe prawe wielkości do 9 mm. Niewielkie zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Mierne pobudzenie metabolicznie w pachwinie lewej na obszarze wielkości 26x14x38 mm SUV max 1,6- w topografii opisywanego poprzednio pakietu węzłowego. Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 4,6- w pierwszej kolejności o charakterze odczynowym. Niejednorodny metabolizm FDG w śledzionie wielkości 124x57x138 mm. Wzmożony metabolizm FDG w topografii trzonu macicy SUV max do 3,7- do kontroli ginekologicznej (OM 09.2020) Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne: - okołoaortalne obustronnie wielkości do 22x14 mm; - przy naczyniach biodrowych wspólnych i wewnętrznych lewych, wielkości do18x12 mm; - przy naczyniach biodrowych zewnętrznych lewych wielkości do 19x22 mm ; - pachwinowe prawe wielkości do 7 mm. Ok. 10mm obwodowa hypodensyjna w przeglądowym badaniu TK zmiana w prawym płacie wątroby - torbielka?</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem SUV max do 3,1- w pierwszej kolejności wynikający ze stosowanego leczenia. Spłycenie fizjologicznych krzywizn kręgosłupa. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa [ciasna na poziomie C5/C6]. Zwapnienie w krążku międzykręgowym na poziomie L5/S1. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Wyspa kostna w prawej kości kulszowej.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź metaboliczną choroby na stosowane leczenie z częściową regresją zmian radiologicznych. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>4.6</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 68 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja lewej zatoki czołowej, hypoplazja prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne węzły chłonne pachowe obustronnie. Niewielkie zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo. Drobny obwodowy pęcherz rozedmowy w segm. 6 płuca lewego.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 3,8- w pierwszej kolejności o charakterze odczynowym. Niejednorodny metabolizm FDG w śledzionie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zmiany włókniste w pachwinie lewej na obszarze wielkości 25x13 mm (SUV max 1,6). Śledziona powiększona: wielkości: 130x76x143mm. Ok. 11mm obwodowa hypodensyjna w przeglądowym badaniu TK zmiana w prawym płacie wątroby - torbielka?  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem - w pierwszej kolejności wynikający z zastosowanego leczenia. Spłycenie fizjologicznych krzywizn kręgosłupa. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa [ciasna na poziomie C5/C6]. Zwapnienie w krążku międzykręgowym na poziomie L5/S1. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Wyspa kostna w prawej kości kulszowej.  Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 2,8.</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja lewej zatoki czołowej, hypoplazja prawej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne węzły chłonne pachowe obustronnie. Niewielkie zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo. Drobny obwodowy pęcherz rozedmowy w segm. 6 płuca lewego.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 3,8- w pierwszej kolejności o charakterze odczynowym. Niejednorodny metabolizm FDG w śledzionie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zmiany włókniste w pachwinie lewej na obszarze wielkości 25x13 mm (SUV max 1,6). Śledziona powiększona: wielkości: 130x76x143mm. Ok. 11mm obwodowa hypodensyjna w przeglądowym badaniu TK zmiana w prawym płacie wątroby - torbielka?</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem - w pierwszej kolejności wynikający z zastosowanego leczenia. Spłycenie fizjologicznych krzywizn kręgosłupa. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa [ciasna na poziomie C5/C6]. Zwapnienie w krążku międzykręgowym na poziomie L5/S1. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Wyspa kostna w prawej kości kulszowej.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności  aktywnej metabolicznie choroby chłoniakowej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58min od podania 18F-FDG. Glikemia: 99mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne grup: - 2A po stronie lewej wielkości wg PET do 16x28mm, SUV max 21,0, - 2A po stronie prawej wielkości wg PET 20x27mm, SUV max 23,2. Symetryczna aktywność metaboliczna w fałdach głosowych, SUV max 4,2 - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja lewej zatoki czołowej, hypoplazja prawej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - przytchawicze prawe górne średnicy wg PET 20mm, SUV max 29,8, - w śródpiersiu tylnym obustronnie na wysokości trzonów kręgów Th2-Th4 o łącznej wielkości wg PET 33x28x46mm, SUV max 35,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne węzły chłonne pachowe obustronnie. Niewielkie zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo. Drobny obwodowy pęcherz rozedmowy w segm. 6 płuca lewego.  Brzuch i miednica: Aktywny metabolicznie pakiet węzłowy we wnęce wątroby średnicy wg PET 30mm, SUV max 19,0. Niejednorodny metabolizm FDG w śledzionie. Rozlana aktywność metaboliczna we wstępnicy, SUV max do 7,3 - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zmiany włókniste w pachwinie lewej na obszarze wielkości 25x13mm (SUV max 1,6). Śledziona powiększona w wymiarze dwubiegunowym 136mm. Ok. 11mm obwodowa hypodensyjna w przeglądowym badaniu TK zmiana w prawym płacie wątroby - torbielka?  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem - w pierwszej kolejności wynikający z zastosowanego leczenia. Spłycenie fizjologicznych krzywizn kręgosłupa. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa [ciasna na poziomie C5/C6]. Zwapnienie w krążku międzykręgowym na poziomie L5/S1. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Wyspa kostna w prawej kości kulszowej.  Wartości referencyjne: MBPS SUVmax 2,3; Prawy płat wątroby SUVmax do 3,2.</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne grup: - 2A po stronie lewej wielkości wg PET do 16x28mm, SUV max 21,0, - 2A po stronie prawej wielkości wg PET 20x27mm, SUV max 23,2. Symetryczna aktywność metaboliczna w fałdach głosowych, SUV max 4,2 - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja lewej zatoki czołowej, hypoplazja prawej.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - przytchawicze prawe górne średnicy wg PET 20mm, SUV max 29,8, - w śródpiersiu tylnym obustronnie na wysokości trzonów kręgów Th2-Th4 o łącznej wielkości wg PET 33x28x46mm, SUV max 35,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne węzły chłonne pachowe obustronnie. Niewielkie zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo. Drobny obwodowy pęcherz rozedmowy w segm. 6 płuca lewego.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie pakiet węzłowy we wnęce wątroby średnicy wg PET 30mm, SUV max 19,0. Niejednorodny metabolizm FDG w śledzionie. Rozlana aktywność metaboliczna we wstępnicy, SUV max do 7,3 - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zmiany włókniste w pachwinie lewej na obszarze wielkości 25x13mm (SUV max 1,6). Śledziona powiększona w wymiarze dwubiegunowym 136mm. Ok. 11mm obwodowa hypodensyjna w przeglądowym badaniu TK zmiana w prawym płacie wątroby - torbielka?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem - w pierwszej kolejności wynikający z zastosowanego leczenia. Spłycenie fizjologicznych krzywizn kręgosłupa. Zmiany zwyrodnieniowe kręgosłupa. Dyskopatie w odcinku szyjnym kręgosłupa [ciasna na poziomie C5/C6]. Zwapnienie w krążku międzykręgowym na poziomie L5/S1. Drobne zmiany zwyrodnieniowo-wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Wyspa kostna w prawej kości kulszowej.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z zajęciem węzłów chłonnych po obu stronach przepony. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>35.6</v>
       </c>
     </row>
